--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-09-29 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:09</t>
+    <t xml:space="preserve">2026-09-29 18:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -572,7 +572,7 @@
         <v>57.85</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>69.21</v>
+        <v>69.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:39</t>
+    <t xml:space="preserve">2026-10-05 04:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -569,7 +569,7 @@
         <v>-11.36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>57.85</v>
+        <v>57.86</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>69.22</v>
